--- a/_907_WeaponsText.xlsx
+++ b/_907_WeaponsText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C172ED-9680-4DDF-81E8-2AE2B9C1D5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE88760-231A-4E96-8764-5891B473F84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -62,233 +62,99 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>골드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp Card</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>経験値カード</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 카드</t>
-  </si>
-  <si>
-    <t>ゴールド</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>크리스탈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crystal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>クリスタル</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>희귀한 마력이 응축된 신비한 결정체.
-캐릭터 소환과 각종 특별 상품 구매에 사용된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A mysterious crystal condensed with rare magical energy.
-Used to summon characters and purchase various special items.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>希少な魔力が凝縮された神秘的な結晶。
-キャラクタ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーの募集や、さまざまな特別商品との交換に使用できる。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어 경험치 카드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Player Exp Card</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>プレイヤ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ー経験値カード</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어의 성장을 돕는 경험치가 담긴 카드.
-획득 시 플레이어 경험치를 얻는다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A card containing experience to aid the player’s growth.
-Grants Player EXP when obtained.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>プレイヤ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーの成長を助ける経験値が込められたカード。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-獲得時にプレイヤ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ー経験値を獲得する。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐릭터와 무기의 성장을 돕는 경험치가 담긴 카드.
-사용 시 선택한 캐릭터 또는 무기의 경험치를 증가시킨다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>キャラクタ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーと武器の成長を助ける経験値が込められたカード。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-使用すると選</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>択したキャラクターまたは武器の経験値が増加する。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A card containing experience to aid the growth of characters and weapons.
-Use it to grant EXP to the selected character or weapon.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 내에서 널리 사용되는 일반 재화.
-캐릭터와 무기의 성장 및 각종 상품 구매에 사용된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A common currency widely used throughout the game.
-Used to upgrade characters and weapons and purchase various items.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>ゲ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーム内で広く使用される一般的な通貨。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-キャラクタ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーや武器の強化、さまざまな商品の購入に使用される。</t>
-    </r>
+    <t>레어 무기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare Weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>レア武器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉽게 구할 수 없으며 일반 무기보다 뛰어난 성능을 지닌 무기입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A hard-to-find weapon with better performance than ordinary weapons.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入手が難しく、一般的な武器よりも優れた性能を持つ武器です。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화된 레어 무기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enhanced Rare Weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化されたレア武器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화를 통해 기존보다 더욱 뛰어난 성능을 갖게 된 레어 무기입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A rare weapon enhanced to deliver even greater performance.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化によって、さらに優れた性能を得たレア武器です。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에픽 무기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic Weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>エピック武器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 힘과 희소성을 지닌 매우 뛰어난 무기입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An exceptional weapon possessing immense power and rarity.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>強大な力と希少性を兼ね備えた、非常に優れた武器です。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary Weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伝説の武器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전설로 전해질 만큼 압도적인 힘과 극도의 희소성을 지닌 무기입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An extraordinarily rare weapon of overwhelming power, worthy of legend.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伝説として語り継がれるほどの圧倒的な力と、極めて高い希少性を持つ武器です。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전설 무기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -360,7 +226,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -377,6 +243,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -714,14 +583,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
   <dimension ref="A2:D54"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="11" width="18.640625" customWidth="1"/>
-    <col min="12" max="34" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5625" customWidth="1"/>
+    <col min="2" max="11" width="18.625" customWidth="1"/>
+    <col min="12" max="34" width="12.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -749,65 +618,65 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
-        <v>9040001</v>
+        <v>9070001</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="67.5" x14ac:dyDescent="0.6">
+      <c r="A5" s="3">
+        <v>9070002</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A6" s="2">
+        <v>9070003</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="123" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3">
-        <v>9040002</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="67.5" x14ac:dyDescent="0.6">
+      <c r="A7" s="3">
+        <v>9070004</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" ht="18.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="2">
-        <v>9040003</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3">
-        <v>9040004</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" ht="18.45" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A8" s="2">
-        <v>9040005</v>
+        <v>9070005</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>18</v>
@@ -819,9 +688,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="92.15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A9" s="3">
-        <v>9040006</v>
+        <v>9070006</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>21</v>
@@ -829,81 +698,81 @@
       <c r="C9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" ht="18.45" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
       <c r="A10" s="2">
-        <v>9040007</v>
+        <v>9070007</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="147.44999999999999" x14ac:dyDescent="0.55000000000000004">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="88.15" x14ac:dyDescent="0.6">
       <c r="A11" s="3">
-        <v>9040008</v>
+        <v>9070008</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+        <v>27</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
